--- a/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3 Composition API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C551D4-0A32-4B27-B1DC-2568449D6DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84C185A-100B-49D9-8D8F-EB526A7887F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7635" yWindow="-18330" windowWidth="23250" windowHeight="12450" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Литература" sheetId="14" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="1733">
   <si>
     <t>Vue</t>
   </si>
@@ -22480,110 +22480,6 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>childComponent</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-&lt;script setup&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>const model = defineModel()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-function </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>() {
-  model.value++
-}
-&lt;/script&gt;
-&lt;template&gt;
-  &lt;div&gt;Parent bound v-model is: {{ model }}&lt;/div&gt;
-  &lt;button @click="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"&gt;Increment&lt;/button&gt;
-&lt;/template&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>rootComponent</t>
     </r>
     <r>
@@ -40784,17 +40680,254 @@
       <t>ВСЕГО ОБЪЕКТА</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>childComponent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&lt;script setup&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>const model = defineModel()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+function </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>() {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //относится </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не к defineModel</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, а к </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ниже</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  model.value++
+}
+&lt;/script&gt;
+&lt;template&gt;
+  &lt;div&gt;Parent bound v-model is: {{ model }}&lt;/div&gt;
+  &lt;button @click="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"&gt;Increment&lt;/button&gt;
+&lt;/template&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Сокращенная запись props</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;filter-panel
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>actionDisabled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        :isCopy="canShareDashboard"
+        :sourceId="sourceId"
+        :mode="mode"
+        :dashboardId="dashboardId"
+        @copy-dashboard-link="copyDashboardLink"
+      &gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В Vue запись actionDisabled без : — это сокращение для </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:actionDisabled="true"</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="85">
+  <fonts count="86">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -41601,13 +41734,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -41618,20 +41751,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41640,122 +41773,122 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="60" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="66" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="67" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -41770,46 +41903,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41818,74 +41951,74 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -41894,97 +42027,97 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="16" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="14" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -42002,22 +42135,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -42029,71 +42162,71 @@
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="75" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="76" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -42102,77 +42235,80 @@
     <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -42181,10 +42317,10 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -42193,25 +42329,25 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -42844,7 +42980,7 @@
     </row>
     <row r="5" spans="1:22">
       <c r="B5" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C5" s="182" t="s">
         <v>789</v>
@@ -42852,10 +42988,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="B6" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C6" s="182" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -42869,40 +43005,40 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="C11" s="182"/>
     </row>
     <row r="12" spans="1:22">
       <c r="B12" s="2" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C12" s="198" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="B13" s="2" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C13" s="199" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="B14" s="2" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="C14" s="199" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="B15" s="2" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="C15" s="199" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -42926,12 +43062,12 @@
         <v>787</v>
       </c>
       <c r="C21" s="188" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="C22" s="109" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -42955,27 +43091,27 @@
         <v>787</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="2" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C33" s="188" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="115.2">
       <c r="C34" s="187" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D24">
     <sortCondition ref="D4:D24"/>
   </sortState>
-  <phoneticPr fontId="40" type="noConversion"/>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -43667,7 +43803,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E34"/>
+  <dimension ref="A2:E36"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.33203125" style="2" customWidth="1"/>
@@ -43708,7 +43844,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="152" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -43764,10 +43900,10 @@
         <v>721</v>
       </c>
       <c r="B14" s="149" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C14" s="152" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D14" s="55" t="s">
         <v>398</v>
@@ -43778,7 +43914,7 @@
         <v>484</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C15" s="102" t="s">
         <v>728</v>
@@ -43795,7 +43931,7 @@
     </row>
     <row r="17" spans="1:4" ht="72">
       <c r="B17" s="154" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>854</v>
@@ -43812,130 +43948,146 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="23" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="345.6">
-      <c r="A20" s="55"/>
+        <v>1730</v>
+      </c>
+      <c r="B19" s="153" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="115.2">
+      <c r="B20" s="92" t="s">
+        <v>1732</v>
+      </c>
       <c r="C20" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>991</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="345.6">
+      <c r="A22" s="55"/>
+      <c r="C22" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="23" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="86.4">
-      <c r="C22" s="2" t="s">
+    <row r="24" spans="1:4" ht="86.4">
+      <c r="C24" s="2" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="43.2">
-      <c r="A23" s="2" t="s">
+    <row r="25" spans="1:4" ht="43.2">
+      <c r="A25" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>741</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="57.6">
-      <c r="A25" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="57.6">
-      <c r="A26" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="57.6">
       <c r="A27" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="57.6">
+      <c r="A28" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="57.6">
+      <c r="A29" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="86.4">
-      <c r="A28" s="2" t="s">
+    <row r="30" spans="1:4" ht="86.4">
+      <c r="A30" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="72">
-      <c r="A29" s="2" t="s">
+    <row r="31" spans="1:4" ht="72">
+      <c r="A31" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="100.8">
-      <c r="A30" s="2" t="s">
+    <row r="32" spans="1:4" ht="100.8">
+      <c r="A32" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D30" s="99" t="s">
+      <c r="D32" s="99" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="23" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" s="23" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="129.6">
-      <c r="C32" s="2" t="s">
+    <row r="34" spans="1:3" ht="129.6">
+      <c r="C34" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="86.4">
-      <c r="A33" s="2" t="s">
+    <row r="35" spans="1:3" ht="86.4">
+      <c r="A35" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="86.4">
-      <c r="A34" s="2" t="s">
+    <row r="36" spans="1:3" ht="86.4">
+      <c r="A36" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>756</v>
       </c>
     </row>
@@ -44551,10 +44703,10 @@
         <v>664</v>
       </c>
       <c r="B31" s="110" t="s">
-        <v>929</v>
-      </c>
-      <c r="C31" s="110" t="s">
         <v>928</v>
+      </c>
+      <c r="C31" s="206" t="s">
+        <v>1729</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>658</v>
@@ -44704,13 +44856,13 @@
     </row>
     <row r="37" spans="1:22" s="7" customFormat="1" ht="244.8">
       <c r="A37" s="22" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B37" s="197" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C37" s="197" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D37" s="68"/>
       <c r="F37" s="1"/>
@@ -44731,13 +44883,13 @@
     </row>
     <row r="38" spans="1:22" s="7" customFormat="1" ht="273.60000000000002">
       <c r="A38" s="197" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B38" s="197" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C38" s="197" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D38" s="68"/>
       <c r="F38" s="1"/>
@@ -46132,17 +46284,17 @@
         <v>181</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="20" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="20" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -46152,7 +46304,7 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="10" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1">
@@ -46179,7 +46331,7 @@
         <v>181</v>
       </c>
       <c r="B11" s="151" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C11" s="114" t="s">
         <v>776</v>
@@ -46190,129 +46342,129 @@
     </row>
     <row r="12" spans="1:21" ht="273.60000000000002">
       <c r="B12" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D12" s="139" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="23" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C13" s="139"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="139" t="s">
+        <v>999</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C14" s="139" t="s">
         <v>1000</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C14" s="139" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="139" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C15" s="139" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="139" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="139" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="139" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C17" s="139" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="139" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C18" s="139" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="139" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C19" s="139" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="139" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C20" s="139" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="23" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:20" ht="28.8">
       <c r="A22" s="141" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B22" s="144" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D22" s="141"/>
     </row>
     <row r="23" spans="1:20" ht="86.4">
       <c r="A23" s="141" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B23" s="144" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="115.2">
@@ -46320,106 +46472,106 @@
         <v>641</v>
       </c>
       <c r="B24" s="140" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C24" s="145" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D24" s="140" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="28.8">
       <c r="A25" s="140" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B25" s="146" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C25" s="145" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D25" s="140" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="140" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B26" s="140" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C26" s="145" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D26" s="140" t="s">
         <v>1011</v>
-      </c>
-      <c r="B26" s="140" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C26" s="145" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D26" s="140" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="140" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B27" s="140" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C27" s="145" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D27" s="140" t="s">
         <v>1015</v>
-      </c>
-      <c r="B27" s="140" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C27" s="145" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D27" s="140" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="187.2">
       <c r="A28" s="140" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B28" s="146" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C28" s="145" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D28" s="140" t="s">
         <v>1038</v>
-      </c>
-      <c r="D28" s="140" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="28.8">
       <c r="A29" s="140" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B29" s="146" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C29" s="145" t="s">
         <v>1020</v>
       </c>
-      <c r="B29" s="146" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C29" s="145" t="s">
-        <v>1021</v>
-      </c>
       <c r="D29" s="140" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="28.8">
       <c r="A30" s="142" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B30" s="144" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C30" s="143" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D30" s="143"/>
     </row>
     <row r="31" spans="1:20" ht="28.8">
       <c r="A31" s="142" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B31" s="144" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C31" s="143" t="s">
         <v>1027</v>
-      </c>
-      <c r="B31" s="144" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C31" s="143" t="s">
-        <v>1028</v>
       </c>
       <c r="D31" s="143"/>
     </row>
@@ -46441,7 +46593,7 @@
     <row r="33" spans="1:20" s="147" customFormat="1" ht="57.6">
       <c r="B33" s="132"/>
       <c r="C33" s="148" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D33" s="149"/>
       <c r="E33" s="3"/>
@@ -46455,10 +46607,10 @@
     <row r="34" spans="1:20" s="147" customFormat="1" ht="186.6" customHeight="1">
       <c r="B34" s="132"/>
       <c r="C34" s="148" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D34" s="148" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="132"/>
@@ -46470,7 +46622,7 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="10" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>2</v>
@@ -46718,25 +46870,25 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="137" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B2" s="87" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="53" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="53" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="53" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="39" customFormat="1">
@@ -46744,80 +46896,80 @@
     </row>
     <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="53" t="s">
+        <v>944</v>
+      </c>
+      <c r="B9" s="113" t="s">
         <v>945</v>
-      </c>
-      <c r="B9" s="113" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="144">
       <c r="C10" s="110" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="20" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2">
       <c r="C12" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1">
       <c r="A13" s="137" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B13" s="113" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8">
       <c r="B15" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="115.2">
       <c r="B17" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="20" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="57.6">
       <c r="B19" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.8">
       <c r="A20" s="20" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B20" s="113" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C20" s="113" t="s">
         <v>62</v>
@@ -46828,106 +46980,106 @@
     </row>
     <row r="21" spans="1:4" ht="43.2">
       <c r="B21" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="20" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="115.2">
       <c r="B25" s="110" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="138" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B26" s="110" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="216">
       <c r="B27" s="110" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="53" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72">
       <c r="B29" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="187.2">
       <c r="B30" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="20" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="86.4">
       <c r="A32" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B32" s="139" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="43.2">
       <c r="A33" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B33" s="139" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="331.2">
       <c r="A34" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B34" s="110" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -47843,16 +47995,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="53" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="86.4">
       <c r="C15" s="87" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D15" s="110" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -47861,7 +48013,7 @@
         <v>647</v>
       </c>
       <c r="D16" s="110" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -47881,7 +48033,7 @@
     </row>
     <row r="18" spans="1:6" s="54" customFormat="1">
       <c r="A18" s="62" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B18" s="55"/>
       <c r="C18" s="55"/>
@@ -47891,7 +48043,7 @@
     </row>
     <row r="19" spans="1:6" s="54" customFormat="1" ht="100.8">
       <c r="A19" s="204" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>593</v>
@@ -47909,7 +48061,7 @@
     </row>
     <row r="20" spans="1:6" s="54" customFormat="1" ht="43.2">
       <c r="A20" s="205" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="55"/>
@@ -47919,13 +48071,13 @@
     </row>
     <row r="21" spans="1:6" s="54" customFormat="1" ht="129.6">
       <c r="A21" s="204" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>591</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="D21" s="58" t="s">
         <v>494</v>
@@ -47935,7 +48087,7 @@
     </row>
     <row r="22" spans="1:6" s="54" customFormat="1" ht="43.2">
       <c r="A22" s="205" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -47949,7 +48101,7 @@
         <v>592</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D23" s="58" t="s">
         <v>495</v>
@@ -47969,7 +48121,7 @@
     </row>
     <row r="25" spans="1:6" ht="86.4">
       <c r="A25" s="204" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>594</v>
@@ -48025,19 +48177,19 @@
         <v>625</v>
       </c>
       <c r="D30" s="110" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="374.4">
       <c r="A31" s="58"/>
       <c r="C31" s="110" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D31" s="110" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E31" s="110" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -48841,37 +48993,37 @@
       <c r="A9" s="55"/>
       <c r="B9" s="55"/>
       <c r="C9" s="183" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E9" s="71"/>
     </row>
     <row r="10" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A10" s="55" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B10" s="55" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C10" s="183" t="s">
         <v>1407</v>
-      </c>
-      <c r="C10" s="183" t="s">
-        <v>1408</v>
       </c>
       <c r="E10" s="71"/>
     </row>
     <row r="11" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A11" s="55" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B11" s="55" t="s">
         <v>1405</v>
       </c>
-      <c r="B11" s="55" t="s">
-        <v>1406</v>
-      </c>
       <c r="C11" s="55" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E11" s="71"/>
     </row>
     <row r="12" spans="1:5" s="54" customFormat="1">
       <c r="A12" s="53" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
@@ -48885,10 +49037,10 @@
         <v>897</v>
       </c>
       <c r="C13" s="54" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D13" s="54" t="s">
         <v>1410</v>
-      </c>
-      <c r="D13" s="54" t="s">
-        <v>1411</v>
       </c>
       <c r="E13" s="71"/>
     </row>
@@ -48937,7 +49089,7 @@
         <v>904</v>
       </c>
       <c r="B19" s="182" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -49068,32 +49220,32 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="23" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="20" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="20" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="20" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="20" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="39" customFormat="1">
@@ -49102,7 +49254,7 @@
     <row r="10" spans="1:6" s="132" customFormat="1"/>
     <row r="11" spans="1:6">
       <c r="A11" s="23" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D11" s="40"/>
       <c r="E11" s="155"/>
@@ -49110,7 +49262,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="20" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D12" s="40"/>
       <c r="E12" s="155"/>
@@ -49118,10 +49270,10 @@
     </row>
     <row r="13" spans="1:6" ht="72">
       <c r="B13" s="175" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C13" s="168" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D13" s="40"/>
       <c r="E13" s="155"/>
@@ -49129,7 +49281,7 @@
     </row>
     <row r="14" spans="1:6" ht="72">
       <c r="C14" s="168" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="155"/>
@@ -49137,13 +49289,13 @@
     </row>
     <row r="15" spans="1:6" ht="28.8">
       <c r="A15" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C15" s="92" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D15" s="40"/>
       <c r="E15" s="155"/>
@@ -49151,13 +49303,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C16" s="92" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D16" s="40"/>
       <c r="E16" s="155"/>
@@ -49165,10 +49317,10 @@
     </row>
     <row r="17" spans="1:6" ht="100.8">
       <c r="B17" s="168" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C17" s="92" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D17" s="40"/>
       <c r="E17" s="155"/>
@@ -49176,7 +49328,7 @@
     </row>
     <row r="18" spans="1:6" ht="100.8">
       <c r="C18" s="92" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D18" s="40"/>
       <c r="E18" s="155"/>
@@ -49184,13 +49336,13 @@
     </row>
     <row r="19" spans="1:6" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B19" s="139" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C19" s="92" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="155"/>
@@ -49198,13 +49350,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D20" s="40"/>
       <c r="E20" s="155"/>
@@ -49212,83 +49364,83 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="72">
       <c r="B23" s="139" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="172.8">
       <c r="C25" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="288">
       <c r="C27" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="20" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B28" s="113" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="331.2">
       <c r="B29" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C29" s="139" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="20" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="158.4">
       <c r="B31" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="20" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="187.2">
       <c r="C33" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="40" type="noConversion"/>
+  <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -49335,50 +49487,50 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="174" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="174" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="174" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D8" s="177" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="196" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="174" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="39" customFormat="1">
@@ -49386,14 +49538,14 @@
     </row>
     <row r="13" spans="1:5" s="132" customFormat="1">
       <c r="C13" s="167" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D13" s="171"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B14" s="168"/>
     </row>
@@ -49403,7 +49555,7 @@
         <v>62</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -49411,7 +49563,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -49419,25 +49571,25 @@
         <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>1281</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="201.6">
       <c r="C19" s="2" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="174" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>62</v>
@@ -49447,80 +49599,80 @@
     </row>
     <row r="21" spans="1:4" ht="72">
       <c r="A21" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="72">
       <c r="A22" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="72">
       <c r="A23" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="167" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8">
       <c r="B25" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1292</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="57.6">
       <c r="B26" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="115.2">
       <c r="A27" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="72">
       <c r="A28" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="167" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
@@ -49528,63 +49680,63 @@
     </row>
     <row r="30" spans="1:4" ht="201.6">
       <c r="C30" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="23" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="43.2">
       <c r="A32" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B32" s="168" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>1304</v>
-      </c>
-      <c r="B32" s="168" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>1305</v>
       </c>
       <c r="D32" s="169"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="175" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="C34" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="302.39999999999998">
       <c r="A36" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B36" s="188" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="28.8">
       <c r="A37" s="176" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B37" s="168" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C37" s="168"/>
     </row>
@@ -49592,212 +49744,212 @@
       <c r="A38" s="168"/>
       <c r="B38" s="168"/>
       <c r="C38" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="175" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="115.2">
       <c r="C40" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="175" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="100.8">
       <c r="C42" s="168" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="115.2">
       <c r="A43" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="115.2">
       <c r="A44" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="144">
       <c r="A45" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="57.6">
       <c r="A46" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="28.8">
       <c r="A47" s="176" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B47" s="168" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="187.2">
       <c r="A48" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="86.4">
       <c r="A49" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B49" s="168" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="B49" s="168" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="175" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>1325</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="72">
       <c r="C51" s="2" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="175" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="187.2">
       <c r="C53" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="45" customHeight="1">
       <c r="A54" s="176" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B54" s="168" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="144">
       <c r="A55" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="72">
       <c r="A56" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>1336</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="129.6">
       <c r="A57" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>1340</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>1339</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="244.8">
       <c r="B58" s="168" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="175" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="C60" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="175" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="172.8">
@@ -49805,7 +49957,7 @@
         <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="144">
@@ -49813,48 +49965,48 @@
         <v>43</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="28.8">
       <c r="A64" s="176" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B64" s="168" t="s">
         <v>1357</v>
       </c>
-      <c r="B64" s="168" t="s">
-        <v>1358</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="216">
       <c r="A65" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>1361</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>1360</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="244.8">
       <c r="A66" s="2" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="175" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="172.8">
@@ -49862,7 +50014,7 @@
         <v>62</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="144">
@@ -49870,92 +50022,92 @@
         <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="23" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="172.8">
       <c r="A71" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B71" s="168" t="s">
         <v>1372</v>
       </c>
-      <c r="B71" s="168" t="s">
-        <v>1373</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="244.8">
       <c r="B72" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="23" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="100.8">
       <c r="A74" s="2" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="115.2">
       <c r="A75" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="244.8">
       <c r="A76" s="2" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="43.2">
       <c r="A77" s="2" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="86.4">
       <c r="C78" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="174" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="216">
       <c r="B80" s="2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>1379</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>1380</v>
       </c>
     </row>
   </sheetData>
@@ -50005,7 +50157,7 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -50026,7 +50178,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="174"/>
       <c r="D8" s="177" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -50040,14 +50192,14 @@
     </row>
     <row r="13" spans="1:5" s="132" customFormat="1">
       <c r="C13" s="167" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="171"/>
       <c r="E13" s="70"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -50097,30 +50249,30 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="167" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C3" s="91" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="23" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -50128,153 +50280,153 @@
     </row>
     <row r="12" spans="1:5" s="132" customFormat="1">
       <c r="C12" s="167" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D12" s="171"/>
       <c r="E12" s="70"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B13" s="168"/>
     </row>
     <row r="14" spans="1:5" ht="72">
       <c r="B14" s="168" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C14" s="192"/>
     </row>
     <row r="15" spans="1:5" ht="302.39999999999998">
       <c r="A15" s="168" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>1274</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="230.4">
       <c r="A17" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B17" s="182" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="201.6">
       <c r="A18" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B18" s="188" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="B18" s="188" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1416</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="100.8">
       <c r="A19" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>1417</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="23" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="273.60000000000002">
       <c r="A21" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B21" s="188" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="158.4">
       <c r="A22" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>1425</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="A23" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="23" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="C24" s="113" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="187.2">
       <c r="C25" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>1604</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="115.2">
       <c r="B26" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>1607</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>1608</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="23" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="115.2">
       <c r="B28" s="188" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1610</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="57.6">
       <c r="D29" s="109" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
   </sheetData>
@@ -50304,84 +50456,84 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="176" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B2" s="176" t="s">
         <v>1469</v>
-      </c>
-      <c r="B2" s="176" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B5" s="189" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="28.8">
       <c r="A6" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B6" s="189" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="C6" s="91" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B7" s="189" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B8" s="189" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B9" s="189" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="21" spans="1:29" s="39" customFormat="1">
@@ -50389,69 +50541,69 @@
     </row>
     <row r="22" spans="1:29" s="132" customFormat="1">
       <c r="C22" s="167" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D22" s="171"/>
       <c r="E22" s="70"/>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="176" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B23" s="149"/>
       <c r="C23" s="149"/>
     </row>
     <row r="24" spans="1:29" ht="43.2">
       <c r="A24" s="113" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B24" s="185" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C24" s="188" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1429</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1430</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="27" spans="1:29" s="70" customFormat="1">
       <c r="A27" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -50480,16 +50632,16 @@
     </row>
     <row r="28" spans="1:29" s="70" customFormat="1">
       <c r="A28" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -50518,16 +50670,16 @@
     </row>
     <row r="29" spans="1:29" s="70" customFormat="1">
       <c r="A29" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -50556,16 +50708,16 @@
     </row>
     <row r="30" spans="1:29" s="70" customFormat="1">
       <c r="A30" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -50594,16 +50746,16 @@
     </row>
     <row r="31" spans="1:29" s="70" customFormat="1">
       <c r="A31" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -50632,16 +50784,16 @@
     </row>
     <row r="32" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A32" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -50670,16 +50822,16 @@
     </row>
     <row r="33" spans="1:29" s="70" customFormat="1">
       <c r="A33" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -50708,16 +50860,16 @@
     </row>
     <row r="34" spans="1:29" s="70" customFormat="1">
       <c r="A34" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -50746,7 +50898,7 @@
     </row>
     <row r="35" spans="1:29" s="70" customFormat="1">
       <c r="A35" s="176" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -50778,10 +50930,10 @@
     </row>
     <row r="36" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A36" s="113" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B36" s="185" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -50812,7 +50964,7 @@
     </row>
     <row r="37" spans="1:29" s="70" customFormat="1">
       <c r="A37" s="23" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -50844,14 +50996,14 @@
     </row>
     <row r="38" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A38" s="185" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B38" s="185" t="s">
         <v>1521</v>
-      </c>
-      <c r="B38" s="185" t="s">
-        <v>1522</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -50880,7 +51032,7 @@
     </row>
     <row r="39" spans="1:29" s="70" customFormat="1">
       <c r="A39" s="23" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -50912,16 +51064,16 @@
     </row>
     <row r="40" spans="1:29" s="70" customFormat="1">
       <c r="A40" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>1473</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>1529</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>1474</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -50950,16 +51102,16 @@
     </row>
     <row r="41" spans="1:29" s="70" customFormat="1">
       <c r="A41" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>1475</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>1477</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -50988,16 +51140,16 @@
     </row>
     <row r="42" spans="1:29" s="70" customFormat="1">
       <c r="A42" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1479</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -51026,16 +51178,16 @@
     </row>
     <row r="43" spans="1:29" s="70" customFormat="1">
       <c r="A43" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>1481</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1482</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -51064,16 +51216,16 @@
     </row>
     <row r="44" spans="1:29" s="70" customFormat="1">
       <c r="A44" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>1484</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>1485</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -51102,16 +51254,16 @@
     </row>
     <row r="45" spans="1:29" s="70" customFormat="1">
       <c r="A45" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>1526</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>1527</v>
-      </c>
       <c r="C45" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D45" s="182" t="s">
         <v>1533</v>
-      </c>
-      <c r="D45" s="182" t="s">
-        <v>1534</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -51140,7 +51292,7 @@
     </row>
     <row r="46" spans="1:29" s="70" customFormat="1">
       <c r="A46" s="189" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B46" s="182"/>
       <c r="C46" s="2"/>
@@ -51172,10 +51324,10 @@
     </row>
     <row r="47" spans="1:29" s="70" customFormat="1">
       <c r="A47" s="113" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B47" s="113" t="s">
         <v>1486</v>
-      </c>
-      <c r="B47" s="113" t="s">
-        <v>1487</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -51207,10 +51359,10 @@
     <row r="48" spans="1:29" s="70" customFormat="1">
       <c r="A48" s="132"/>
       <c r="B48" s="189" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C48" s="23" t="s">
         <v>1554</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>1555</v>
       </c>
       <c r="D48" s="2"/>
       <c r="F48" s="2"/>
@@ -51240,16 +51392,16 @@
     </row>
     <row r="49" spans="1:29" s="70" customFormat="1" ht="43.2">
       <c r="A49" s="182" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B49" s="188" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>1538</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -51278,7 +51430,7 @@
     </row>
     <row r="50" spans="1:29" s="70" customFormat="1">
       <c r="A50" s="190" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B50" s="182"/>
       <c r="C50" s="2"/>
@@ -51310,13 +51462,13 @@
     </row>
     <row r="51" spans="1:29" s="70" customFormat="1">
       <c r="A51" s="2" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D51" s="2"/>
       <c r="F51" s="2"/>
@@ -51346,16 +51498,16 @@
     </row>
     <row r="52" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D52" s="188" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -51385,13 +51537,13 @@
     <row r="53" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A53" s="2"/>
       <c r="B53" s="188" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C53" s="182" t="s">
         <v>1547</v>
       </c>
-      <c r="C53" s="182" t="s">
-        <v>1548</v>
-      </c>
       <c r="D53" s="188" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -51421,13 +51573,13 @@
     <row r="54" spans="1:29" s="70" customFormat="1" ht="72">
       <c r="A54" s="2"/>
       <c r="B54" s="59" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C54" s="59" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D54" s="188" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -51457,13 +51609,13 @@
     <row r="55" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A55" s="2"/>
       <c r="B55" s="59" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D55" s="188" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -51492,13 +51644,13 @@
     </row>
     <row r="56" spans="1:29" s="70" customFormat="1">
       <c r="A56" s="2" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D56" s="188"/>
       <c r="F56" s="2"/>
@@ -51528,7 +51680,7 @@
     </row>
     <row r="57" spans="1:29" s="70" customFormat="1">
       <c r="A57" s="190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="22"/>
@@ -51560,13 +51712,13 @@
     </row>
     <row r="58" spans="1:29" s="70" customFormat="1">
       <c r="A58" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D58" s="2"/>
       <c r="F58" s="2"/>
@@ -51596,13 +51748,13 @@
     </row>
     <row r="59" spans="1:29" s="70" customFormat="1">
       <c r="A59" s="2" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D59" s="188"/>
       <c r="F59" s="2"/>
@@ -51632,16 +51784,16 @@
     </row>
     <row r="60" spans="1:29" s="70" customFormat="1">
       <c r="A60" s="2" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D60" s="188" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -51671,10 +51823,10 @@
     <row r="61" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A61" s="2"/>
       <c r="B61" s="188" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C61" s="182" t="s">
         <v>1547</v>
-      </c>
-      <c r="C61" s="182" t="s">
-        <v>1548</v>
       </c>
       <c r="D61" s="188"/>
       <c r="F61" s="2"/>
@@ -51734,13 +51886,13 @@
     </row>
     <row r="63" spans="1:29" s="70" customFormat="1">
       <c r="A63" s="2" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D63" s="188"/>
       <c r="F63" s="2"/>
@@ -51771,13 +51923,13 @@
     <row r="64" spans="1:29" s="70" customFormat="1" ht="86.4">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D64" s="188" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -51806,10 +51958,10 @@
     </row>
     <row r="65" spans="1:29" s="70" customFormat="1">
       <c r="A65" s="113" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B65" s="113" t="s">
         <v>1488</v>
-      </c>
-      <c r="B65" s="113" t="s">
-        <v>1489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -51841,10 +51993,10 @@
     <row r="66" spans="1:29" s="70" customFormat="1">
       <c r="A66" s="191"/>
       <c r="B66" s="189" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C66" s="23" t="s">
         <v>1554</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>1555</v>
       </c>
       <c r="D66" s="2"/>
       <c r="F66" s="2"/>
@@ -51874,16 +52026,16 @@
     </row>
     <row r="67" spans="1:29" s="70" customFormat="1" ht="57.6">
       <c r="A67" s="182" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B67" s="188" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>1540</v>
-      </c>
       <c r="D67" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -51912,14 +52064,14 @@
     </row>
     <row r="68" spans="1:29" s="70" customFormat="1">
       <c r="A68" s="113" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B68" s="113" t="s">
         <v>1490</v>
-      </c>
-      <c r="B68" s="113" t="s">
-        <v>1491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -51949,10 +52101,10 @@
     <row r="69" spans="1:29" s="70" customFormat="1" ht="172.8">
       <c r="A69" s="2"/>
       <c r="B69" s="188" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
@@ -51982,16 +52134,16 @@
     </row>
     <row r="70" spans="1:29" s="70" customFormat="1">
       <c r="A70" s="113" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B70" s="113" t="s">
         <v>1493</v>
       </c>
-      <c r="B70" s="113" t="s">
-        <v>1494</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -52020,16 +52172,16 @@
     </row>
     <row r="71" spans="1:29" s="70" customFormat="1">
       <c r="A71" s="113" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B71" s="113" t="s">
         <v>1495</v>
       </c>
-      <c r="B71" s="113" t="s">
-        <v>1496</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -52058,7 +52210,7 @@
     </row>
     <row r="72" spans="1:29" s="70" customFormat="1" ht="28.8">
       <c r="A72" s="189" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -52090,14 +52242,14 @@
     </row>
     <row r="73" spans="1:29" s="70" customFormat="1">
       <c r="A73" s="113" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B73" s="113" t="s">
         <v>1499</v>
-      </c>
-      <c r="B73" s="113" t="s">
-        <v>1500</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -52126,13 +52278,13 @@
     </row>
     <row r="74" spans="1:29" s="70" customFormat="1" ht="115.2">
       <c r="A74" s="188" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B74" s="188" t="s">
         <v>1584</v>
       </c>
-      <c r="B74" s="188" t="s">
-        <v>1585</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="D74" s="2"/>
       <c r="F74" s="2"/>
@@ -52162,7 +52314,7 @@
     </row>
     <row r="75" spans="1:29" s="70" customFormat="1">
       <c r="A75" s="189" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B75" s="188"/>
       <c r="C75" s="2"/>
@@ -52194,124 +52346,124 @@
     </row>
     <row r="76" spans="1:29" ht="216">
       <c r="B76" s="59" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C76" s="188" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D76" s="188" t="s">
         <v>1595</v>
-      </c>
-      <c r="C76" s="188" t="s">
-        <v>1593</v>
-      </c>
-      <c r="D76" s="188" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="77" spans="1:29">
       <c r="A77" s="185" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B77" s="185" t="s">
         <v>1501</v>
       </c>
-      <c r="B77" s="185" t="s">
-        <v>1502</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="78" spans="1:29">
       <c r="A78" s="189" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="79" spans="1:29">
       <c r="A79" s="185" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B79" s="185" t="s">
         <v>1503</v>
       </c>
-      <c r="B79" s="185" t="s">
+      <c r="D79" s="2" t="s">
         <v>1504</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="80" spans="1:29">
       <c r="A80" s="189" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="185" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B81" s="185" t="s">
         <v>1506</v>
       </c>
-      <c r="B81" s="185" t="s">
+      <c r="D81" s="2" t="s">
         <v>1507</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="184" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B82" s="185" t="s">
         <v>1497</v>
       </c>
-      <c r="B82" s="185" t="s">
-        <v>1498</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="216">
       <c r="B83" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="189" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="185" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B85" s="185" t="s">
         <v>1509</v>
       </c>
-      <c r="B85" s="185" t="s">
+      <c r="D85" s="2" t="s">
         <v>1510</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="185" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B86" s="185" t="s">
         <v>1512</v>
       </c>
-      <c r="B86" s="185" t="s">
+      <c r="D86" s="2" t="s">
         <v>1513</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="185" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B87" s="185" t="s">
         <v>1515</v>
       </c>
-      <c r="B87" s="185" t="s">
+      <c r="D87" s="2" t="s">
         <v>1516</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="185" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B88" s="185" t="s">
         <v>1518</v>
       </c>
-      <c r="B88" s="185" t="s">
+      <c r="D88" s="2" t="s">
         <v>1519</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -52383,163 +52535,163 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="C4" s="203" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="C5" s="4" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="C6" s="4" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="C7" s="4" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="C8" s="4" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="C9" s="4" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="C10" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="C11" s="4" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="C12" s="4" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="C13" s="4" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="C14" s="4" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="C15" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="C16" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" s="4" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" s="4" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" s="4" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" s="4" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" s="4" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" s="4" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" s="4" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" s="4" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" s="4" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" s="4" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="29" spans="3:3">
       <c r="C29" s="4" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" s="4" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" s="4" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="32" spans="3:3">
       <c r="C32" s="4" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" s="4" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
   </sheetData>
@@ -52588,71 +52740,71 @@
         <v>530</v>
       </c>
       <c r="B2" s="158" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1113</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="62" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D3" s="109" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" s="62" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="62" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="62" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="62" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="62" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="62" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="62" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="62" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -52662,17 +52814,17 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="62" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="62" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="62" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="39" customFormat="1">
@@ -52699,7 +52851,7 @@
     </row>
     <row r="23" spans="1:5" s="54" customFormat="1">
       <c r="A23" s="62" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="55"/>
@@ -52707,19 +52859,19 @@
     </row>
     <row r="24" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="B24" s="157" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D24" s="157" t="s">
         <v>1116</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D24" s="157" t="s">
-        <v>1117</v>
       </c>
       <c r="E24" s="71"/>
     </row>
     <row r="25" spans="1:5" s="54" customFormat="1" ht="86.4">
       <c r="B25" s="157" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C25" s="55"/>
       <c r="D25" s="157"/>
@@ -52727,7 +52879,7 @@
     </row>
     <row r="26" spans="1:5" s="54" customFormat="1">
       <c r="A26" s="62" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B26" s="55"/>
       <c r="E26" s="71"/>
@@ -52735,16 +52887,16 @@
     <row r="27" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A27" s="55"/>
       <c r="B27" s="164" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C27" s="69" t="s">
         <v>1185</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>1186</v>
       </c>
       <c r="E27" s="71"/>
     </row>
     <row r="28" spans="1:5" s="54" customFormat="1">
       <c r="A28" s="62" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
@@ -52755,317 +52907,317 @@
       <c r="A29" s="55"/>
       <c r="B29" s="55"/>
       <c r="C29" s="152" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="71"/>
     </row>
     <row r="30" spans="1:5" s="54" customFormat="1">
       <c r="A30" s="165" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B30" s="165" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C30" s="165" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="71"/>
     </row>
     <row r="31" spans="1:5" s="54" customFormat="1">
       <c r="A31" s="165" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B31" s="165" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C31" s="165" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D31" s="55"/>
       <c r="E31" s="71"/>
     </row>
     <row r="32" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A32" s="158" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B32" s="139" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="71"/>
     </row>
     <row r="33" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A33" s="62" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C33" s="55"/>
       <c r="D33" s="55" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E33" s="71"/>
     </row>
     <row r="34" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A34" s="55" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C34" s="136" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="71"/>
     </row>
     <row r="35" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A35" s="55" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C35" s="136" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D35" s="55"/>
       <c r="E35" s="71"/>
     </row>
     <row r="36" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A36" s="55" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C36" s="136" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D36" s="55"/>
       <c r="E36" s="71"/>
     </row>
     <row r="37" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A37" s="55" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C37" s="136" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D37" s="55"/>
       <c r="E37" s="71"/>
     </row>
     <row r="38" spans="1:5" s="54" customFormat="1" ht="72">
       <c r="A38" s="55" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C38" s="136" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D38" s="55"/>
       <c r="E38" s="71"/>
     </row>
     <row r="39" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A39" s="55" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C39" s="136" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D39" s="55"/>
       <c r="E39" s="71"/>
     </row>
     <row r="40" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A40" s="62" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="55" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E40" s="71"/>
     </row>
     <row r="41" spans="1:5" s="54" customFormat="1" ht="129.6">
       <c r="A41" s="55"/>
       <c r="B41" s="54" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C41" s="152" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D41" s="55" t="s">
         <v>1105</v>
-      </c>
-      <c r="D41" s="55" t="s">
-        <v>1106</v>
       </c>
       <c r="E41" s="71"/>
     </row>
     <row r="42" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A42" s="55"/>
       <c r="B42" s="54" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="E42" s="71"/>
     </row>
     <row r="43" spans="1:5" s="54" customFormat="1" ht="244.8">
       <c r="A43" s="55"/>
       <c r="B43" s="54" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C43" s="152" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D43" s="55" t="s">
         <v>1110</v>
-      </c>
-      <c r="D43" s="55" t="s">
-        <v>1111</v>
       </c>
       <c r="E43" s="71"/>
     </row>
     <row r="44" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A44" s="62" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D44" s="54" t="s">
         <v>1128</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>1129</v>
       </c>
       <c r="E44" s="71"/>
     </row>
     <row r="45" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="B45" s="157" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C45" s="54" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E45" s="71"/>
     </row>
     <row r="46" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A46" s="62" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="55"/>
       <c r="D46" s="55" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E46" s="71"/>
     </row>
     <row r="47" spans="1:5" s="54" customFormat="1" ht="302.39999999999998">
       <c r="A47" s="55"/>
       <c r="B47" s="152" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E47" s="71"/>
     </row>
     <row r="48" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A48" s="62" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="55"/>
       <c r="D48" s="55" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E48" s="71"/>
     </row>
     <row r="49" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A49" s="55"/>
       <c r="B49" s="152" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D49" s="55"/>
       <c r="E49" s="71"/>
     </row>
     <row r="50" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A50" s="62" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C50" s="55"/>
       <c r="D50" s="55" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E50" s="71"/>
     </row>
     <row r="51" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A51" s="159" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B51" s="152" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D51" s="55"/>
       <c r="E51" s="71"/>
     </row>
     <row r="52" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A52" s="62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="55"/>
       <c r="D52" s="55" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E52" s="71"/>
     </row>
     <row r="53" spans="1:5" s="54" customFormat="1" ht="144">
       <c r="A53" s="160" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B53" s="162" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C53" s="162" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D53" s="55"/>
       <c r="E53" s="71"/>
     </row>
     <row r="54" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A54" s="62" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B54" s="55"/>
       <c r="C54" s="55"/>
       <c r="D54" s="55" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E54" s="71"/>
     </row>
     <row r="55" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A55" s="55"/>
       <c r="B55" s="55" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C55" s="55" t="s">
         <v>1149</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>1150</v>
       </c>
       <c r="D55" s="55"/>
       <c r="E55" s="71"/>
     </row>
     <row r="56" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A56" s="62" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B56" s="55"/>
       <c r="C56" s="55"/>
       <c r="D56" s="55" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E56" s="71"/>
     </row>
     <row r="57" spans="1:5" s="54" customFormat="1" ht="172.8">
       <c r="A57" s="55"/>
       <c r="B57" s="55" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C57" s="55" t="s">
         <v>1152</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>1153</v>
       </c>
       <c r="D57" s="55"/>
       <c r="E57" s="71"/>
@@ -53077,17 +53229,17 @@
       <c r="B58" s="53"/>
       <c r="C58" s="53"/>
       <c r="D58" s="53" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E58" s="71"/>
     </row>
     <row r="59" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A59" s="55"/>
       <c r="B59" s="162" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D59" s="55"/>
       <c r="E59" s="71"/>
@@ -53095,17 +53247,17 @@
     <row r="60" spans="1:5" s="54" customFormat="1" ht="100.8">
       <c r="A60" s="55"/>
       <c r="B60" s="164" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D60" s="55"/>
       <c r="E60" s="71"/>
     </row>
     <row r="61" spans="1:5" s="54" customFormat="1">
       <c r="A61" s="163" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B61" s="55"/>
       <c r="C61" s="55"/>
@@ -53116,7 +53268,7 @@
       <c r="A62" s="55"/>
       <c r="B62" s="55"/>
       <c r="C62" s="55" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D62" s="55"/>
       <c r="E62" s="71"/>
@@ -53125,7 +53277,7 @@
       <c r="A63" s="55"/>
       <c r="B63" s="55"/>
       <c r="C63" s="55" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D63" s="55"/>
       <c r="E63" s="71"/>
@@ -53134,7 +53286,7 @@
       <c r="A64" s="55"/>
       <c r="B64" s="55"/>
       <c r="C64" s="55" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D64" s="55"/>
       <c r="E64" s="71"/>
@@ -53147,10 +53299,10 @@
     </row>
     <row r="66" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A66" s="62" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C66" s="55"/>
       <c r="D66" s="55"/>
@@ -53160,19 +53312,19 @@
       <c r="A67" s="55"/>
       <c r="B67" s="55"/>
       <c r="C67" s="55" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D67" s="55" t="s">
         <v>1164</v>
-      </c>
-      <c r="D67" s="55" t="s">
-        <v>1165</v>
       </c>
       <c r="E67" s="71"/>
     </row>
     <row r="68" spans="1:5" s="54" customFormat="1">
       <c r="A68" s="62" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E68" s="71"/>
     </row>
@@ -53181,29 +53333,29 @@
       <c r="B69" s="55"/>
       <c r="C69" s="55"/>
       <c r="D69" s="164" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E69" s="71"/>
     </row>
     <row r="70" spans="1:5" s="54" customFormat="1" ht="16.2" customHeight="1">
       <c r="A70" s="62" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B70" s="54" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C70" s="163" t="s">
         <v>1170</v>
-      </c>
-      <c r="B70" s="54" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C70" s="163" t="s">
-        <v>1171</v>
       </c>
       <c r="E70" s="71"/>
     </row>
     <row r="71" spans="1:5" s="54" customFormat="1" ht="216">
       <c r="A71" s="55"/>
       <c r="B71" s="55" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E71" s="71"/>
     </row>
@@ -53255,12 +53407,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -53270,22 +53422,22 @@
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="141" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="141" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="167" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="167" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="39" customFormat="1">
@@ -53293,58 +53445,58 @@
     </row>
     <row r="12" spans="1:5" s="132" customFormat="1">
       <c r="C12" s="167" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D13" s="169" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="100.8">
       <c r="B14" s="168" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="216.6" customHeight="1">
       <c r="B15" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>1189</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D16" s="169" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="86.4">
       <c r="B17" s="168" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="129.6">
       <c r="B18" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
@@ -53352,71 +53504,71 @@
         <v>468</v>
       </c>
       <c r="B19" s="168" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D19" s="169" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="141" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="115.2">
       <c r="B21" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>1211</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="141" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="100.8">
       <c r="B23" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
       <c r="A24" s="167" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D24" s="169" t="s">
         <v>1200</v>
-      </c>
-      <c r="D24" s="169" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="201.6">
       <c r="A25" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B25" s="168" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1202</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="167" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D26" s="169" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
       <c r="B27" s="168" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1206</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1207</v>
       </c>
     </row>
   </sheetData>
@@ -53473,20 +53625,20 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="167" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="167" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="39" customFormat="1">
@@ -53494,112 +53646,112 @@
     </row>
     <row r="7" spans="1:5" s="132" customFormat="1">
       <c r="C7" s="167" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D7" s="170" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="70"/>
     </row>
     <row r="8" spans="1:5" ht="28.8">
       <c r="A8" s="23" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B8" s="168" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2">
       <c r="C9" s="168" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="158.4">
       <c r="B10" s="168" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="158.4">
       <c r="B11" s="168" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>1218</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="167" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72">
       <c r="B13" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="167" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B14" s="113" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="100.8">
       <c r="C15" s="168" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="86.4">
       <c r="A16" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="216">
       <c r="A17" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C17" s="168" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="216">
       <c r="B18" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C18" s="168" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="167" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D19" s="169" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="86.4">
       <c r="B20" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>1236</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -53653,12 +53805,12 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="167" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -53669,10 +53821,10 @@
     </row>
     <row r="7" spans="1:5" s="132" customFormat="1">
       <c r="C7" s="167" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D7" s="171" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="70"/>
     </row>
@@ -53683,108 +53835,108 @@
     </row>
     <row r="9" spans="1:5" ht="129.6">
       <c r="B9" s="168" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1244</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="167" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6">
       <c r="B11" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8">
       <c r="B12" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>1247</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="86.4">
       <c r="B13" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>1250</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="167" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="C15" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C16" s="172" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30">
       <c r="A17" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C17" s="173" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30">
       <c r="A18" s="2" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C18" s="173" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="316.8">
       <c r="B19" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="167" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="144">
       <c r="B21" s="168" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="172.8">
       <c r="B22" s="168" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>1268</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -53840,25 +53992,25 @@
     <row r="3" spans="1:5">
       <c r="A3" s="130"/>
       <c r="B3" s="106" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="130"/>
       <c r="B4" s="106" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="130"/>
       <c r="B5" s="106" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="130"/>
       <c r="B6" s="106" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -53899,7 +54051,7 @@
         <v>502</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C13" s="55" t="s">
         <v>503</v>
@@ -53909,7 +54061,7 @@
     </row>
     <row r="14" spans="1:5" s="54" customFormat="1">
       <c r="A14" s="62" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B14" s="55"/>
       <c r="C14" s="55"/>
@@ -53919,10 +54071,10 @@
     <row r="15" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A15" s="55"/>
       <c r="B15" s="55" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D15" s="55"/>
       <c r="E15" s="71"/>
@@ -53930,10 +54082,10 @@
     <row r="16" spans="1:5" s="54" customFormat="1" ht="28.8">
       <c r="A16" s="55"/>
       <c r="B16" s="55" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C16" s="136" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="71"/>
@@ -53941,10 +54093,10 @@
     <row r="17" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A17" s="55"/>
       <c r="B17" s="55" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="71"/>
@@ -53952,17 +54104,17 @@
     <row r="18" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A18" s="55"/>
       <c r="B18" s="55" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C18" s="136" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="71"/>
     </row>
     <row r="19" spans="1:5" s="54" customFormat="1">
       <c r="A19" s="62" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -53972,10 +54124,10 @@
     <row r="20" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A20" s="55"/>
       <c r="B20" s="55" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C20" s="136" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D20" s="55"/>
       <c r="E20" s="71"/>
@@ -53983,10 +54135,10 @@
     <row r="21" spans="1:5" s="54" customFormat="1" ht="57.6">
       <c r="A21" s="55"/>
       <c r="B21" s="55" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C21" s="136" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D21" s="55"/>
       <c r="E21" s="71"/>
@@ -53994,10 +54146,10 @@
     <row r="22" spans="1:5" s="54" customFormat="1" ht="43.2">
       <c r="A22" s="55"/>
       <c r="B22" s="55" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C22" s="136" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="71"/>
@@ -54007,7 +54159,7 @@
         <v>504</v>
       </c>
       <c r="B23" s="95" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E23" s="71"/>
     </row>
@@ -54278,156 +54430,156 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="C4" s="203" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="10" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B5" s="92" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C5" s="92" t="s">
         <v>1660</v>
-      </c>
-      <c r="C5" s="92" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="43.2">
       <c r="A6" s="92" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="92" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="43.2">
       <c r="A7" s="92" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="92" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="43.2">
       <c r="A8" s="92" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="92" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="43.2">
       <c r="A9" s="92" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="92" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="28.8">
       <c r="A10" s="92" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="92" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="43.2">
       <c r="A11" s="92" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="92" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="28.8">
       <c r="A12" s="92" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="92" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="43.2">
       <c r="A13" s="92" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="92" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="28.8">
       <c r="A14" s="92" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="92" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="28.8">
       <c r="A15" s="92" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="92" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="28.8">
       <c r="A16" s="92" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="92" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="28.8">
       <c r="A17" s="92" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="92" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="28.8">
       <c r="A18" s="92" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="92" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="28.8">
       <c r="A19" s="92" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="92" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28.8">
       <c r="A20" s="92" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="92" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
   </sheetData>
@@ -54494,10 +54646,10 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -54524,7 +54676,7 @@
         <v>706</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="C7" s="98" t="s">
         <v>707</v>
@@ -54540,13 +54692,13 @@
     </row>
     <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C9" s="193" t="s">
         <v>1616</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1627</v>
-      </c>
-      <c r="C9" s="193" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -54559,65 +54711,65 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="10" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="C14" s="194" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C15" s="194" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="10" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" ht="28.8">
       <c r="A17" s="1" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="C17" s="195" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="C18" s="194" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="57.6">
       <c r="A19" s="10" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>1624</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1625</v>
-      </c>
       <c r="C19" s="194" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="10" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C20" s="194" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -55030,7 +55182,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="200" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="B2" s="89"/>
       <c r="C2" s="89"/>
@@ -55038,7 +55190,7 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="200" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B3" s="89"/>
       <c r="C3" s="89"/>
@@ -55213,10 +55365,10 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" s="23" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B21" s="184" t="s">
         <v>1650</v>
-      </c>
-      <c r="B21" s="184" t="s">
-        <v>1651</v>
       </c>
       <c r="C21" s="114" t="s">
         <v>777</v>
@@ -55229,13 +55381,13 @@
     <row r="22" spans="1:22" ht="409.6">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C22" s="201" t="s">
         <v>1652</v>
       </c>
-      <c r="C22" s="201" t="s">
+      <c r="D22" s="2" t="s">
         <v>1653</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1654</v>
       </c>
       <c r="P22" s="73"/>
       <c r="U22" s="73"/>
@@ -55519,7 +55671,7 @@
         <v>784</v>
       </c>
       <c r="B22" s="117" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -55530,13 +55682,13 @@
     <row r="23" spans="1:22">
       <c r="A23" s="178"/>
       <c r="B23" s="179" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C23" s="180" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D23" s="181" t="s">
         <v>1397</v>
-      </c>
-      <c r="D23" s="181" t="s">
-        <v>1398</v>
       </c>
       <c r="P23" s="73"/>
       <c r="U23" s="73"/>
@@ -55667,7 +55819,7 @@
         <v>823</v>
       </c>
       <c r="C34" s="202" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -55825,7 +55977,7 @@
         <v>367</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -56168,7 +56320,7 @@
         <v>316</v>
       </c>
       <c r="B33" s="161" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>370</v>
